--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  23.06.2025 a 29.06.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  23.06.2025 a 29.06.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DABBA595-0A64-489D-9628-97385939754B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F65F617-68E0-4101-975C-E8D1F6D6383A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="23.06" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="131">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -312,6 +312,145 @@
   </si>
   <si>
     <t xml:space="preserve">BELCHIOR DE BRITO FARIAS ME                  </t>
+  </si>
+  <si>
+    <t>18/06/2025</t>
+  </si>
+  <si>
+    <t>26/06/2025</t>
+  </si>
+  <si>
+    <t>LIMBO</t>
+  </si>
+  <si>
+    <t>KLEUBER ANTONIO DE CARVALHO MOTTA CPF  11663855820</t>
+  </si>
+  <si>
+    <t>Sem retorno do cliente</t>
+  </si>
+  <si>
+    <t>MARCELO TEIXEIRA MARTINS CPF 53911423934</t>
+  </si>
+  <si>
+    <t>Duplicidade;</t>
+  </si>
+  <si>
+    <t>Renovação de outro corretor sem cancelamento</t>
+  </si>
+  <si>
+    <t>13/06/2025</t>
+  </si>
+  <si>
+    <t>Vagner Abrantes Soares Da Silva CPF 38235977877</t>
+  </si>
+  <si>
+    <t>24/06/2025</t>
+  </si>
+  <si>
+    <t>JOSE RIBEIRO FILHO CPF 4248449820</t>
+  </si>
+  <si>
+    <t>O ano modelo informado não corresponde ao chassi do veículo.</t>
+  </si>
+  <si>
+    <t>TALITA ALMEIDA RODRIGUES CPF 4702296329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Não existe código FIPE para este chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TARCILA ADRIANA FARIAS DE OLIVEIRA           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBIRAJARA ANTONIO DOS SANTOS                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FABIANA APARECIDA ALLELUIA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAIME TELIS PACHECO DE FREITAS FILHO         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADRIANA DE SOUZA MENEZES                     </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não há po
+ssibilidade de efetuar a transferência de bônus para o(a) senhor(a
+) ADRIANA DE SOUZA MENEZES, pois este não consta como condutor na
+apólice anterior.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOLTEC NE SERVICOS METALURGICOS REPARACAO DE </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não há po
+ssibilidade de efetuar a transferência de bônus para o(a) senhor(a
+) JOSE CARLOS DE SOUZA OLIVEIRA, pois este não consta no quadro so
+cietário do segurado/empresa anterior MOLTEC NE SERVICOS METALURGI
+COS REPARAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANOEL FORTE DE MELO                         </t>
+  </si>
+  <si>
+    <t>Santander - Bônus correto deve ser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATRICIA PARISI ALTIERI                      </t>
+  </si>
+  <si>
+    <t>F
+avor enviar cópia completa da apólice anterior 2024/2025 (atual) a
+través desse e-mail.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LETICIA MARIA BASSO DE LIMA                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SILVANA MARQUESANI                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACILDA PRATA                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSAENE SANTOS ANDRADE                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANTONIO JOSE LEITE DE CARVALHO               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULO ROGERIO DO AMARAL                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVANEIDE GOMES SOUSA                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SWILLIAM LUDTKE CAPISCH                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROGERIO BARBOSA                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAIANA DA SILVA CORREIA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDRO ANGELO SOARES                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALDECY CARDOSO MOREIRA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAISON SCHMITT ROCHA                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALDENIR JOSE DOS SANTOS                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCISKARLA DE ARAUJO AZEVEDO CABRAL SOUZA  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALESANDRO PEREIRA DOS SANTOS JUNIOR          </t>
   </si>
 </sst>
 </file>
@@ -360,7 +499,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -485,12 +624,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -553,15 +705,28 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -2871,13 +3036,13 @@
       <c r="C2" s="19">
         <v>45833</v>
       </c>
-      <c r="D2" s="28">
+      <c r="D2" s="22">
         <v>133022249</v>
       </c>
       <c r="E2" s="18">
         <v>2578492191</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="12" t="s">
         <v>66</v>
       </c>
       <c r="G2" s="20" t="s">
@@ -2900,13 +3065,13 @@
       <c r="C3" s="19">
         <v>45833</v>
       </c>
-      <c r="D3" s="28">
+      <c r="D3" s="22">
         <v>133016638</v>
       </c>
       <c r="E3" s="18">
         <v>3450007429</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="F3" s="12" t="s">
         <v>67</v>
       </c>
       <c r="G3" s="20" t="s">
@@ -2929,13 +3094,13 @@
       <c r="C4" s="19">
         <v>45833</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="22">
         <v>133004445</v>
       </c>
       <c r="E4" s="18">
         <v>3450006440</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="12" t="s">
         <v>68</v>
       </c>
       <c r="G4" s="20" t="s">
@@ -2958,13 +3123,13 @@
       <c r="C5" s="19">
         <v>45833</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="22">
         <v>133021281</v>
       </c>
       <c r="E5" s="18">
         <v>3450007814</v>
       </c>
-      <c r="F5" s="26" t="s">
+      <c r="F5" s="12" t="s">
         <v>69</v>
       </c>
       <c r="G5" s="20" t="s">
@@ -2987,19 +3152,19 @@
       <c r="C6" s="19">
         <v>45833</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="22">
         <v>133036268</v>
       </c>
       <c r="E6" s="18">
         <v>3450008881</v>
       </c>
-      <c r="F6" s="26" t="s">
+      <c r="F6" s="12" t="s">
         <v>70</v>
       </c>
       <c r="G6" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="30" t="s">
+      <c r="H6" s="9" t="s">
         <v>71</v>
       </c>
       <c r="I6" s="23">
@@ -3016,13 +3181,13 @@
       <c r="C7" s="19">
         <v>45833</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="22">
         <v>133038310</v>
       </c>
       <c r="E7" s="18">
         <v>3450009035</v>
       </c>
-      <c r="F7" s="26" t="s">
+      <c r="F7" s="12" t="s">
         <v>72</v>
       </c>
       <c r="G7" s="20" t="s">
@@ -3045,19 +3210,19 @@
       <c r="C8" s="19">
         <v>45833</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="22">
         <v>133032350</v>
       </c>
       <c r="E8" s="18">
         <v>3450008562</v>
       </c>
-      <c r="F8" s="26" t="s">
+      <c r="F8" s="12" t="s">
         <v>73</v>
       </c>
       <c r="G8" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="31" t="s">
+      <c r="H8" s="10" t="s">
         <v>74</v>
       </c>
       <c r="I8" s="23">
@@ -3074,19 +3239,19 @@
       <c r="C9" s="19">
         <v>45833</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="22">
         <v>133027814</v>
       </c>
       <c r="E9" s="18">
         <v>3450008166</v>
       </c>
-      <c r="F9" s="26" t="s">
+      <c r="F9" s="12" t="s">
         <v>75</v>
       </c>
       <c r="G9" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="30" t="s">
+      <c r="H9" s="9" t="s">
         <v>76</v>
       </c>
       <c r="I9" s="23">
@@ -3103,19 +3268,19 @@
       <c r="C10" s="19">
         <v>45833</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="22">
         <v>133052365</v>
       </c>
       <c r="E10" s="18">
         <v>3450009750</v>
       </c>
-      <c r="F10" s="26" t="s">
+      <c r="F10" s="12" t="s">
         <v>77</v>
       </c>
       <c r="G10" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H10" s="30" t="s">
+      <c r="H10" s="9" t="s">
         <v>78</v>
       </c>
       <c r="I10" s="23">
@@ -3132,19 +3297,19 @@
       <c r="C11" s="19">
         <v>45833</v>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="22">
         <v>133104287</v>
       </c>
       <c r="E11" s="18">
         <v>3450012489</v>
       </c>
-      <c r="F11" s="26" t="s">
+      <c r="F11" s="12" t="s">
         <v>79</v>
       </c>
       <c r="G11" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="H11" s="30" t="s">
+      <c r="H11" s="9" t="s">
         <v>30</v>
       </c>
       <c r="I11" s="23">
@@ -3161,19 +3326,19 @@
       <c r="C12" s="19">
         <v>45833</v>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="22">
         <v>133101251</v>
       </c>
       <c r="E12" s="18">
         <v>3450012313</v>
       </c>
-      <c r="F12" s="26" t="s">
+      <c r="F12" s="12" t="s">
         <v>80</v>
       </c>
       <c r="G12" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="H12" s="30" t="s">
+      <c r="H12" s="9" t="s">
         <v>30</v>
       </c>
       <c r="I12" s="23">
@@ -3190,19 +3355,19 @@
       <c r="C13" s="19">
         <v>45833</v>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="22">
         <v>133054036</v>
       </c>
       <c r="E13" s="18">
         <v>3450008254</v>
       </c>
-      <c r="F13" s="26" t="s">
+      <c r="F13" s="12" t="s">
         <v>81</v>
       </c>
       <c r="G13" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="30" t="s">
+      <c r="H13" s="9" t="s">
         <v>30</v>
       </c>
       <c r="I13" s="23">
@@ -3219,19 +3384,19 @@
       <c r="C14" s="19">
         <v>45833</v>
       </c>
-      <c r="D14" s="28">
+      <c r="D14" s="22">
         <v>133057676</v>
       </c>
       <c r="E14" s="18">
         <v>3450010168</v>
       </c>
-      <c r="F14" s="26" t="s">
+      <c r="F14" s="12" t="s">
         <v>82</v>
       </c>
       <c r="G14" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="30" t="s">
+      <c r="H14" s="9" t="s">
         <v>30</v>
       </c>
       <c r="I14" s="23">
@@ -3248,19 +3413,19 @@
       <c r="C15" s="19">
         <v>45833</v>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="22">
         <v>133010146</v>
       </c>
       <c r="E15" s="18">
         <v>3450006880</v>
       </c>
-      <c r="F15" s="26" t="s">
+      <c r="F15" s="12" t="s">
         <v>83</v>
       </c>
       <c r="G15" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="H15" s="29" t="s">
+      <c r="H15" s="27" t="s">
         <v>16</v>
       </c>
       <c r="I15" s="23">
@@ -3277,19 +3442,19 @@
       <c r="C16" s="19">
         <v>45833</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="22">
         <v>133011327</v>
       </c>
       <c r="E16" s="18">
         <v>2578490310</v>
       </c>
-      <c r="F16" s="26" t="s">
+      <c r="F16" s="12" t="s">
         <v>84</v>
       </c>
       <c r="G16" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="29" t="s">
+      <c r="H16" s="27" t="s">
         <v>16</v>
       </c>
       <c r="I16" s="23">
@@ -3306,19 +3471,19 @@
       <c r="C17" s="19">
         <v>45833</v>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="22">
         <v>133013688</v>
       </c>
       <c r="E17" s="18">
         <v>3450007231</v>
       </c>
-      <c r="F17" s="26" t="s">
+      <c r="F17" s="12" t="s">
         <v>85</v>
       </c>
       <c r="G17" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="H17" s="29" t="s">
+      <c r="H17" s="27" t="s">
         <v>16</v>
       </c>
       <c r="I17" s="23">
@@ -3335,19 +3500,19 @@
       <c r="C18" s="19">
         <v>45833</v>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="22">
         <v>133015065</v>
       </c>
       <c r="E18" s="18">
         <v>3450007308</v>
       </c>
-      <c r="F18" s="26" t="s">
+      <c r="F18" s="12" t="s">
         <v>86</v>
       </c>
       <c r="G18" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="H18" s="29" t="s">
+      <c r="H18" s="27" t="s">
         <v>16</v>
       </c>
       <c r="I18" s="23">
@@ -3364,19 +3529,19 @@
       <c r="C19" s="19">
         <v>45833</v>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="22">
         <v>133021474</v>
       </c>
       <c r="E19" s="18">
         <v>3450007825</v>
       </c>
-      <c r="F19" s="26" t="s">
+      <c r="F19" s="12" t="s">
         <v>87</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="H19" s="29" t="s">
+      <c r="H19" s="27" t="s">
         <v>16</v>
       </c>
       <c r="I19" s="23">
@@ -3389,7 +3554,7 @@
       <c r="C20" s="7"/>
       <c r="D20" s="21"/>
       <c r="E20" s="24"/>
-      <c r="F20" s="27"/>
+      <c r="F20" s="26"/>
       <c r="G20" s="6"/>
       <c r="H20" s="9"/>
       <c r="I20" s="23"/>
@@ -3810,15 +3975,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43D38813-FAE5-45C6-9D51-7607EDAA916D}">
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.5703125" customWidth="1"/>
-    <col min="5" max="5" width="24.28515625" customWidth="1"/>
-    <col min="6" max="6" width="36" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" customWidth="1"/>
+    <col min="6" max="6" width="40.85546875" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="42" customWidth="1"/>
     <col min="9" max="9" width="18.7109375" style="17" bestFit="1" customWidth="1"/>
@@ -3857,378 +4022,872 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="9"/>
+      <c r="B2" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" s="18">
+        <v>3450008584</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>92</v>
+      </c>
       <c r="I2"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="9"/>
+      <c r="B3" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" s="18">
+        <v>3450008661</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>95</v>
+      </c>
       <c r="I3"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="9"/>
+      <c r="B4" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450005471</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>12</v>
+      </c>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="9"/>
+      <c r="B5" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" s="18">
+        <v>3450012456</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="H5" s="36" t="s">
+        <v>100</v>
+      </c>
       <c r="I5" s="11"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="9"/>
+      <c r="B6" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3450012016</v>
+      </c>
+      <c r="F6" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="H6" s="36" t="s">
+        <v>102</v>
+      </c>
       <c r="I6" s="11"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="11"/>
+      <c r="B7" s="7">
+        <v>45825</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" s="35">
+        <v>133020014</v>
+      </c>
+      <c r="E7" s="18">
+        <v>3450007737</v>
+      </c>
+      <c r="F7" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="23">
+        <v>45831</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="11"/>
+      <c r="B8" s="7">
+        <v>45826</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" s="35">
+        <v>133027027</v>
+      </c>
+      <c r="E8" s="18">
+        <v>3450008078</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="23">
+        <v>45826</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="11"/>
+      <c r="B9" s="7">
+        <v>45826</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" s="35">
+        <v>133039213</v>
+      </c>
+      <c r="E9" s="18">
+        <v>3450009167</v>
+      </c>
+      <c r="F9" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="23">
+        <v>45826</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="11"/>
+      <c r="B10" s="7">
+        <v>45826</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D10" s="35">
+        <v>133030152</v>
+      </c>
+      <c r="E10" s="18">
+        <v>3450008375</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="23">
+        <v>45826</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="11"/>
+      <c r="B11" s="7">
+        <v>45845</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11" s="35">
+        <v>133090611</v>
+      </c>
+      <c r="E11" s="18">
+        <v>3450011730</v>
+      </c>
+      <c r="F11" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="I11" s="23">
+        <v>45834</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="11"/>
+      <c r="A12" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="7">
+        <v>45828</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" s="35">
+        <v>133103112</v>
+      </c>
+      <c r="E12" s="18">
+        <v>3450010531</v>
+      </c>
+      <c r="F12" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="G12" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="I12" s="23">
+        <v>45834</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="11"/>
+      <c r="B13" s="7">
+        <v>45817</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" s="35">
+        <v>132974835</v>
+      </c>
+      <c r="E13" s="18">
+        <v>3450005691</v>
+      </c>
+      <c r="F13" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="I13" s="23">
+        <v>45817</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="11"/>
+      <c r="B14" s="7">
+        <v>45834</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" s="35">
+        <v>133132930</v>
+      </c>
+      <c r="E14" s="18">
+        <v>3450014238</v>
+      </c>
+      <c r="F14" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="23">
+        <v>45834</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="11"/>
+      <c r="B15" s="7">
+        <v>45829</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" s="35">
+        <v>132967091</v>
+      </c>
+      <c r="E15" s="18">
+        <v>3450005229</v>
+      </c>
+      <c r="F15" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="I15" s="23">
+        <v>45825</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="11"/>
+      <c r="B16" s="7">
+        <v>45832</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" s="35">
+        <v>133054354</v>
+      </c>
+      <c r="E16" s="18">
+        <v>3450008320</v>
+      </c>
+      <c r="F16" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I16" s="23">
+        <v>45832</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="11"/>
+      <c r="B17" s="7">
+        <v>45826</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" s="35">
+        <v>133027559</v>
+      </c>
+      <c r="E17" s="18">
+        <v>3450008122</v>
+      </c>
+      <c r="F17" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I17" s="23">
+        <v>45831</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="11"/>
+      <c r="B18" s="7">
+        <v>45826</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18" s="35">
+        <v>133025490</v>
+      </c>
+      <c r="E18" s="18">
+        <v>3450007946</v>
+      </c>
+      <c r="F18" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="23">
+        <v>45826</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="11"/>
+      <c r="B19" s="7">
+        <v>45826</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" s="35">
+        <v>133027435</v>
+      </c>
+      <c r="E19" s="18">
+        <v>3450008100</v>
+      </c>
+      <c r="F19" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" s="23">
+        <v>45826</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="9"/>
-      <c r="I20"/>
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45826</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20" s="35">
+        <v>133029421</v>
+      </c>
+      <c r="E20" s="18">
+        <v>3450008298</v>
+      </c>
+      <c r="F20" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="23">
+        <v>45826</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="9"/>
-      <c r="I21"/>
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45826</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D21" s="35">
+        <v>133031512</v>
+      </c>
+      <c r="E21" s="18">
+        <v>3450008474</v>
+      </c>
+      <c r="F21" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" s="23">
+        <v>45826</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="9"/>
-      <c r="I22"/>
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45826</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" s="35">
+        <v>133031614</v>
+      </c>
+      <c r="E22" s="18">
+        <v>3450008496</v>
+      </c>
+      <c r="F22" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="23">
+        <v>45826</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="9"/>
-      <c r="I23"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>45826</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D23" s="35">
+        <v>133032552</v>
+      </c>
+      <c r="E23" s="18">
+        <v>3450008617</v>
+      </c>
+      <c r="F23" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" s="23">
+        <v>45826</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="9"/>
-      <c r="I24"/>
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>45825</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D24" s="35">
+        <v>133035269</v>
+      </c>
+      <c r="E24" s="18">
+        <v>3450006857</v>
+      </c>
+      <c r="F24" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="23">
+        <v>45825</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="9"/>
-      <c r="I25"/>
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>45825</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D25" s="35">
+        <v>133035371</v>
+      </c>
+      <c r="E25" s="18">
+        <v>3450006978</v>
+      </c>
+      <c r="F25" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" s="23">
+        <v>45825</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="9"/>
-      <c r="I26"/>
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>45826</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" s="35">
+        <v>133035554</v>
+      </c>
+      <c r="E26" s="18">
+        <v>3450008793</v>
+      </c>
+      <c r="F26" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" s="23">
+        <v>45826</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="9"/>
-      <c r="I27"/>
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="7">
+        <v>45826</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" s="35">
+        <v>133035749</v>
+      </c>
+      <c r="E27" s="18">
+        <v>3450008815</v>
+      </c>
+      <c r="F27" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" s="23">
+        <v>45826</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="9"/>
-      <c r="I28"/>
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="7">
+        <v>45820</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" s="35">
+        <v>133037610</v>
+      </c>
+      <c r="E28" s="18">
+        <v>3450004217</v>
+      </c>
+      <c r="F28" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28" s="23">
+        <v>45820</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="9"/>
-      <c r="I29"/>
+      <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="7">
+        <v>45826</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D29" s="35">
+        <v>133038562</v>
+      </c>
+      <c r="E29" s="18">
+        <v>3450009090</v>
+      </c>
+      <c r="F29" s="30" t="s">
+        <v>128</v>
+      </c>
+      <c r="G29" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I29" s="23">
+        <v>45826</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="9"/>
-      <c r="I30"/>
+      <c r="A30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="7">
+        <v>45826</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D30" s="35">
+        <v>133038981</v>
+      </c>
+      <c r="E30" s="18">
+        <v>3450009145</v>
+      </c>
+      <c r="F30" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="G30" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I30" s="23">
+        <v>45826</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="9"/>
-      <c r="I31"/>
+      <c r="A31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="7">
+        <v>45826</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D31" s="35">
+        <v>133040551</v>
+      </c>
+      <c r="E31" s="18">
+        <v>3450009321</v>
+      </c>
+      <c r="F31" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="G31" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" s="23">
+        <v>45826</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
       <c r="B32" s="8"/>
       <c r="C32" s="7"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="9"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="15"/>
       <c r="G32" s="6"/>
       <c r="H32" s="9"/>
-      <c r="I32"/>
+      <c r="I32" s="23"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
@@ -4239,7 +4898,7 @@
       <c r="F33" s="9"/>
       <c r="G33" s="6"/>
       <c r="H33" s="9"/>
-      <c r="I33"/>
+      <c r="I33" s="23"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="6"/>
@@ -4483,28 +5142,17 @@
       <c r="H55" s="9"/>
       <c r="I55"/>
     </row>
-    <row r="56" spans="1:9">
-      <c r="A56" s="6"/>
-      <c r="B56" s="8"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="9"/>
-      <c r="I56"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="1">
+    <cfRule type="notContainsBlanks" priority="10">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A19" xr:uid="{33F609D2-9B9D-4D52-B406-6DFCF1363D87}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A31" xr:uid="{33F609D2-9B9D-4D52-B406-6DFCF1363D87}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G42" xr:uid="{1B2A036A-428B-43C6-B539-9B85A74E7043}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{1B2A036A-428B-43C6-B539-9B85A74E7043}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6506,110 +7154,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-470939</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-470939</Url>
-      <Description>QAFFA7D2F2TC-2102087286-470939</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="43" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="abf1b9912853fe4a934dbc2373304754">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d8d96f03b10d24171ef462918d18284e" ns1:_="" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="43" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="32fbec5585ae01a22f32af5838af0c4d">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7b2552458edfdc024ce707f91c2c891f" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
     <xsd:import namespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea"/>
     <xsd:import namespace="ea6c6725-5210-4d6a-93cc-4cf85111ac5e"/>
@@ -6657,12 +7203,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Propriedades da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Ação de IU da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
@@ -6671,12 +7217,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Document ID Value" ma:description="The value of the document ID assigned to this item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
+    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Valor do ID do Documento" ma:description="O valor do ID do documento atribuído a este item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="Document ID" ma:description="Permanent link to this document." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
+    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="ID do Documento" ma:description="Ligação permanente a este documento." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:URL">
@@ -6759,7 +7305,7 @@
         <xsd:restriction base="dms:DateTime"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Partilhado Com" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -6778,7 +7324,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Detalhes de Partilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -6811,7 +7357,7 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de Imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -6889,8 +7435,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -6979,18 +7525,120 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-470939</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-470939</Url>
+      <Description>QAFFA7D2F2TC-2102087286-470939</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3038F9CE-9A61-437C-8B23-BB723DA81F89}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75FBB85C-E500-466F-A910-4F2EB96A6878}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>